--- a/artfynd/A 25789-2022 artfynd.xlsx
+++ b/artfynd/A 25789-2022 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>117076039</v>
       </c>
       <c r="B2" t="n">
-        <v>57201</v>
+        <v>57276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 25789-2022 artfynd.xlsx
+++ b/artfynd/A 25789-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117076039</v>
       </c>
       <c r="B2" t="n">
-        <v>57276</v>
+        <v>57277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25789-2022 artfynd.xlsx
+++ b/artfynd/A 25789-2022 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 25789-2022 artfynd.xlsx
+++ b/artfynd/A 25789-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117076039</v>
       </c>
       <c r="B2" t="n">
-        <v>57277</v>
+        <v>57285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25789-2022 artfynd.xlsx
+++ b/artfynd/A 25789-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117076039</v>
       </c>
       <c r="B2" t="n">
-        <v>57294</v>
+        <v>57299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
